--- a/results/standard/UNEP-EGR-2026-total-luc-differences.xlsx
+++ b/results/standard/UNEP-EGR-2026-total-luc-differences.xlsx
@@ -933,27 +933,25 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1990</v>
+        <v>2024</v>
       </c>
       <c r="B36" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" t="n">
-        <v>5.47269895333333</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C36"/>
       <c r="D36" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
       </c>
       <c r="C37" t="n">
-        <v>5.43254206</v>
+        <v>5.47269895333333</v>
       </c>
       <c r="D37" t="s">
         <v>13</v>
@@ -961,13 +959,13 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B38" t="s">
         <v>14</v>
       </c>
       <c r="C38" t="n">
-        <v>5.46352055333333</v>
+        <v>5.43254206</v>
       </c>
       <c r="D38" t="s">
         <v>13</v>
@@ -975,13 +973,13 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
       </c>
       <c r="C39" t="n">
-        <v>5.44559095666667</v>
+        <v>5.46352055333333</v>
       </c>
       <c r="D39" t="s">
         <v>13</v>
@@ -989,13 +987,13 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
       </c>
       <c r="C40" t="n">
-        <v>5.78975107333333</v>
+        <v>5.44559095666667</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
@@ -1003,13 +1001,13 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="B41" t="s">
         <v>14</v>
       </c>
       <c r="C41" t="n">
-        <v>5.83261873333333</v>
+        <v>5.78975107333333</v>
       </c>
       <c r="D41" t="s">
         <v>13</v>
@@ -1017,13 +1015,13 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
       </c>
       <c r="C42" t="n">
-        <v>6.13812796666667</v>
+        <v>5.83261873333333</v>
       </c>
       <c r="D42" t="s">
         <v>13</v>
@@ -1031,13 +1029,13 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
       </c>
       <c r="C43" t="n">
-        <v>7.64181781</v>
+        <v>6.13812796666667</v>
       </c>
       <c r="D43" t="s">
         <v>13</v>
@@ -1045,13 +1043,13 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
       </c>
       <c r="C44" t="n">
-        <v>6.04985091333333</v>
+        <v>7.64181781</v>
       </c>
       <c r="D44" t="s">
         <v>13</v>
@@ -1059,13 +1057,13 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="B45" t="s">
         <v>14</v>
       </c>
       <c r="C45" t="n">
-        <v>6.20889635666667</v>
+        <v>6.04985091333333</v>
       </c>
       <c r="D45" t="s">
         <v>13</v>
@@ -1073,13 +1071,13 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
       </c>
       <c r="C46" t="n">
-        <v>5.9006002</v>
+        <v>6.20889635666667</v>
       </c>
       <c r="D46" t="s">
         <v>13</v>
@@ -1087,13 +1085,13 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
       </c>
       <c r="C47" t="n">
-        <v>5.55939989</v>
+        <v>5.9006002</v>
       </c>
       <c r="D47" t="s">
         <v>13</v>
@@ -1101,13 +1099,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
       </c>
       <c r="C48" t="n">
-        <v>5.78893384666667</v>
+        <v>5.55939989</v>
       </c>
       <c r="D48" t="s">
         <v>13</v>
@@ -1115,13 +1113,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
       </c>
       <c r="C49" t="n">
-        <v>5.94117267333333</v>
+        <v>5.78893384666667</v>
       </c>
       <c r="D49" t="s">
         <v>13</v>
@@ -1129,13 +1127,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
       </c>
       <c r="C50" t="n">
-        <v>5.83714820333333</v>
+        <v>5.94117267333333</v>
       </c>
       <c r="D50" t="s">
         <v>13</v>
@@ -1143,13 +1141,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B51" t="s">
         <v>14</v>
       </c>
       <c r="C51" t="n">
-        <v>5.40539281333333</v>
+        <v>5.83714820333333</v>
       </c>
       <c r="D51" t="s">
         <v>13</v>
@@ -1157,13 +1155,13 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B52" t="s">
         <v>14</v>
       </c>
       <c r="C52" t="n">
-        <v>5.93150671666667</v>
+        <v>5.40539281333333</v>
       </c>
       <c r="D52" t="s">
         <v>13</v>
@@ -1171,13 +1169,13 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B53" t="s">
         <v>14</v>
       </c>
       <c r="C53" t="n">
-        <v>5.24794083</v>
+        <v>5.93150671666667</v>
       </c>
       <c r="D53" t="s">
         <v>13</v>
@@ -1185,13 +1183,13 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
       </c>
       <c r="C54" t="n">
-        <v>5.42179748</v>
+        <v>5.24794083</v>
       </c>
       <c r="D54" t="s">
         <v>13</v>
@@ -1199,13 +1197,13 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B55" t="s">
         <v>14</v>
       </c>
       <c r="C55" t="n">
-        <v>5.86868802666667</v>
+        <v>5.42179748</v>
       </c>
       <c r="D55" t="s">
         <v>13</v>
@@ -1213,13 +1211,13 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
       </c>
       <c r="C56" t="n">
-        <v>5.88447999333333</v>
+        <v>5.86868802666667</v>
       </c>
       <c r="D56" t="s">
         <v>13</v>
@@ -1227,13 +1225,13 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B57" t="s">
         <v>14</v>
       </c>
       <c r="C57" t="n">
-        <v>5.86054747666667</v>
+        <v>5.88447999333333</v>
       </c>
       <c r="D57" t="s">
         <v>13</v>
@@ -1241,13 +1239,13 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B58" t="s">
         <v>14</v>
       </c>
       <c r="C58" t="n">
-        <v>5.80169953</v>
+        <v>5.86054747666667</v>
       </c>
       <c r="D58" t="s">
         <v>13</v>
@@ -1255,13 +1253,13 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B59" t="s">
         <v>14</v>
       </c>
       <c r="C59" t="n">
-        <v>5.63677851</v>
+        <v>5.80169953</v>
       </c>
       <c r="D59" t="s">
         <v>13</v>
@@ -1269,13 +1267,13 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
       </c>
       <c r="C60" t="n">
-        <v>5.74526927333333</v>
+        <v>5.63677851</v>
       </c>
       <c r="D60" t="s">
         <v>13</v>
@@ -1283,13 +1281,13 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B61" t="s">
         <v>14</v>
       </c>
       <c r="C61" t="n">
-        <v>6.07730753666667</v>
+        <v>5.74526927333333</v>
       </c>
       <c r="D61" t="s">
         <v>13</v>
@@ -1297,13 +1295,13 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
       </c>
       <c r="C62" t="n">
-        <v>5.01368222666667</v>
+        <v>6.07730753666667</v>
       </c>
       <c r="D62" t="s">
         <v>13</v>
@@ -1311,13 +1309,13 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
       </c>
       <c r="C63" t="n">
-        <v>4.89656915</v>
+        <v>5.01368222666667</v>
       </c>
       <c r="D63" t="s">
         <v>13</v>
@@ -1325,13 +1323,13 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B64" t="s">
         <v>14</v>
       </c>
       <c r="C64" t="n">
-        <v>4.75922421333333</v>
+        <v>4.89656915</v>
       </c>
       <c r="D64" t="s">
         <v>13</v>
@@ -1339,13 +1337,13 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B65" t="s">
         <v>14</v>
       </c>
       <c r="C65" t="n">
-        <v>4.76127058</v>
+        <v>4.75922421333333</v>
       </c>
       <c r="D65" t="s">
         <v>13</v>
@@ -1353,13 +1351,13 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B66" t="s">
         <v>14</v>
       </c>
       <c r="C66" t="n">
-        <v>4.28816058</v>
+        <v>4.76127058</v>
       </c>
       <c r="D66" t="s">
         <v>13</v>
@@ -1367,13 +1365,13 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B67" t="s">
         <v>14</v>
       </c>
       <c r="C67" t="n">
-        <v>4.40085107</v>
+        <v>4.28816058</v>
       </c>
       <c r="D67" t="s">
         <v>13</v>
@@ -1381,13 +1379,13 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B68" t="s">
         <v>14</v>
       </c>
       <c r="C68" t="n">
-        <v>4.4544346</v>
+        <v>4.40085107</v>
       </c>
       <c r="D68" t="s">
         <v>13</v>
@@ -1395,13 +1393,13 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B69" t="s">
         <v>14</v>
       </c>
       <c r="C69" t="n">
-        <v>4.44131394666667</v>
+        <v>4.4544346</v>
       </c>
       <c r="D69" t="s">
         <v>13</v>
@@ -1409,13 +1407,13 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1990</v>
+        <v>2023</v>
       </c>
       <c r="B70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C70" t="n">
-        <v>5.65162326666667</v>
+        <v>4.44131394666667</v>
       </c>
       <c r="D70" t="s">
         <v>13</v>
@@ -1423,27 +1421,25 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1991</v>
+        <v>2024</v>
       </c>
       <c r="B71" t="s">
-        <v>15</v>
-      </c>
-      <c r="C71" t="n">
-        <v>5.64418543333333</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C71"/>
       <c r="D71" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="B72" t="s">
         <v>15</v>
       </c>
       <c r="C72" t="n">
-        <v>5.92618568666667</v>
+        <v>5.65162326666667</v>
       </c>
       <c r="D72" t="s">
         <v>13</v>
@@ -1451,13 +1447,13 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="B73" t="s">
         <v>15</v>
       </c>
       <c r="C73" t="n">
-        <v>5.58023205666667</v>
+        <v>5.64418543333333</v>
       </c>
       <c r="D73" t="s">
         <v>13</v>
@@ -1465,13 +1461,13 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="B74" t="s">
         <v>15</v>
       </c>
       <c r="C74" t="n">
-        <v>6.79738671333333</v>
+        <v>5.92618568666667</v>
       </c>
       <c r="D74" t="s">
         <v>13</v>
@@ -1479,13 +1475,13 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="B75" t="s">
         <v>15</v>
       </c>
       <c r="C75" t="n">
-        <v>6.04052229</v>
+        <v>5.58023205666667</v>
       </c>
       <c r="D75" t="s">
         <v>13</v>
@@ -1493,13 +1489,13 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="B76" t="s">
         <v>15</v>
       </c>
       <c r="C76" t="n">
-        <v>6.29940215666667</v>
+        <v>6.79738671333333</v>
       </c>
       <c r="D76" t="s">
         <v>13</v>
@@ -1507,13 +1503,13 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="B77" t="s">
         <v>15</v>
       </c>
       <c r="C77" t="n">
-        <v>7.75471623666667</v>
+        <v>6.04052229</v>
       </c>
       <c r="D77" t="s">
         <v>13</v>
@@ -1521,13 +1517,13 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="B78" t="s">
         <v>15</v>
       </c>
       <c r="C78" t="n">
-        <v>6.65798092666667</v>
+        <v>6.29940215666667</v>
       </c>
       <c r="D78" t="s">
         <v>13</v>
@@ -1535,13 +1531,13 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="B79" t="s">
         <v>15</v>
       </c>
       <c r="C79" t="n">
-        <v>6.16069116666667</v>
+        <v>7.75471623666667</v>
       </c>
       <c r="D79" t="s">
         <v>13</v>
@@ -1549,13 +1545,13 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="B80" t="s">
         <v>15</v>
       </c>
       <c r="C80" t="n">
-        <v>5.65965191</v>
+        <v>6.65798092666667</v>
       </c>
       <c r="D80" t="s">
         <v>13</v>
@@ -1563,13 +1559,13 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="B81" t="s">
         <v>15</v>
       </c>
       <c r="C81" t="n">
-        <v>4.85736056666667</v>
+        <v>6.16069116666667</v>
       </c>
       <c r="D81" t="s">
         <v>13</v>
@@ -1577,13 +1573,13 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="B82" t="s">
         <v>15</v>
       </c>
       <c r="C82" t="n">
-        <v>5.80063333666667</v>
+        <v>5.65965191</v>
       </c>
       <c r="D82" t="s">
         <v>13</v>
@@ -1591,13 +1587,13 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="B83" t="s">
         <v>15</v>
       </c>
       <c r="C83" t="n">
-        <v>7.77744429</v>
+        <v>4.85736056666667</v>
       </c>
       <c r="D83" t="s">
         <v>13</v>
@@ -1605,13 +1601,13 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="B84" t="s">
         <v>15</v>
       </c>
       <c r="C84" t="n">
-        <v>6.32239032333333</v>
+        <v>5.80063333666667</v>
       </c>
       <c r="D84" t="s">
         <v>13</v>
@@ -1619,13 +1615,13 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="B85" t="s">
         <v>15</v>
       </c>
       <c r="C85" t="n">
-        <v>5.82975664333333</v>
+        <v>7.77744429</v>
       </c>
       <c r="D85" t="s">
         <v>13</v>
@@ -1633,13 +1629,13 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B86" t="s">
         <v>15</v>
       </c>
       <c r="C86" t="n">
-        <v>5.64007568666667</v>
+        <v>6.32239032333333</v>
       </c>
       <c r="D86" t="s">
         <v>13</v>
@@ -1647,13 +1643,13 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B87" t="s">
         <v>15</v>
       </c>
       <c r="C87" t="n">
-        <v>5.42251226</v>
+        <v>5.82975664333333</v>
       </c>
       <c r="D87" t="s">
         <v>13</v>
@@ -1661,13 +1657,13 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="B88" t="s">
         <v>15</v>
       </c>
       <c r="C88" t="n">
-        <v>5.89702945333333</v>
+        <v>5.64007568666667</v>
       </c>
       <c r="D88" t="s">
         <v>13</v>
@@ -1675,13 +1671,13 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B89" t="s">
         <v>15</v>
       </c>
       <c r="C89" t="n">
-        <v>6.46719351666667</v>
+        <v>5.42251226</v>
       </c>
       <c r="D89" t="s">
         <v>13</v>
@@ -1689,13 +1685,13 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B90" t="s">
         <v>15</v>
       </c>
       <c r="C90" t="n">
-        <v>6.42580224</v>
+        <v>5.89702945333333</v>
       </c>
       <c r="D90" t="s">
         <v>13</v>
@@ -1703,13 +1699,13 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B91" t="s">
         <v>15</v>
       </c>
       <c r="C91" t="n">
-        <v>6.40544241333333</v>
+        <v>6.46719351666667</v>
       </c>
       <c r="D91" t="s">
         <v>13</v>
@@ -1717,13 +1713,13 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B92" t="s">
         <v>15</v>
       </c>
       <c r="C92" t="n">
-        <v>6.94471928333333</v>
+        <v>6.42580224</v>
       </c>
       <c r="D92" t="s">
         <v>13</v>
@@ -1731,13 +1727,13 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="B93" t="s">
         <v>15</v>
       </c>
       <c r="C93" t="n">
-        <v>6.24805195666667</v>
+        <v>6.40544241333333</v>
       </c>
       <c r="D93" t="s">
         <v>13</v>
@@ -1745,13 +1741,13 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="B94" t="s">
         <v>15</v>
       </c>
       <c r="C94" t="n">
-        <v>6.31488685666667</v>
+        <v>6.94471928333333</v>
       </c>
       <c r="D94" t="s">
         <v>13</v>
@@ -1759,13 +1755,13 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B95" t="s">
         <v>15</v>
       </c>
       <c r="C95" t="n">
-        <v>6.16623531333333</v>
+        <v>6.24805195666667</v>
       </c>
       <c r="D95" t="s">
         <v>13</v>
@@ -1773,13 +1769,13 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B96" t="s">
         <v>15</v>
       </c>
       <c r="C96" t="n">
-        <v>4.90856670333333</v>
+        <v>6.31488685666667</v>
       </c>
       <c r="D96" t="s">
         <v>13</v>
@@ -1787,13 +1783,13 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B97" t="s">
         <v>15</v>
       </c>
       <c r="C97" t="n">
-        <v>4.78891534</v>
+        <v>6.16623531333333</v>
       </c>
       <c r="D97" t="s">
         <v>13</v>
@@ -1801,13 +1797,13 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B98" t="s">
         <v>15</v>
       </c>
       <c r="C98" t="n">
-        <v>4.16948029666667</v>
+        <v>4.90856670333333</v>
       </c>
       <c r="D98" t="s">
         <v>13</v>
@@ -1815,13 +1811,13 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="B99" t="s">
         <v>15</v>
       </c>
       <c r="C99" t="n">
-        <v>4.25908083333333</v>
+        <v>4.78891534</v>
       </c>
       <c r="D99" t="s">
         <v>13</v>
@@ -1829,13 +1825,13 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="B100" t="s">
         <v>15</v>
       </c>
       <c r="C100" t="n">
-        <v>3.99461652333333</v>
+        <v>4.16948029666667</v>
       </c>
       <c r="D100" t="s">
         <v>13</v>
@@ -1843,13 +1839,13 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B101" t="s">
         <v>15</v>
       </c>
       <c r="C101" t="n">
-        <v>4.34862197</v>
+        <v>4.25908083333333</v>
       </c>
       <c r="D101" t="s">
         <v>13</v>
@@ -1857,13 +1853,13 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B102" t="s">
         <v>15</v>
       </c>
       <c r="C102" t="n">
-        <v>4.52993544666667</v>
+        <v>3.99461652333333</v>
       </c>
       <c r="D102" t="s">
         <v>13</v>
@@ -1871,13 +1867,13 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B103" t="s">
         <v>15</v>
       </c>
       <c r="C103" t="n">
-        <v>4.48269770666667</v>
+        <v>4.34862197</v>
       </c>
       <c r="D103" t="s">
         <v>13</v>
@@ -1885,13 +1881,13 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1990</v>
+        <v>2022</v>
       </c>
       <c r="B104" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C104" t="n">
-        <v>5.83332072888889</v>
+        <v>4.52993544666667</v>
       </c>
       <c r="D104" t="s">
         <v>13</v>
@@ -1899,13 +1895,13 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1991</v>
+        <v>2023</v>
       </c>
       <c r="B105" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C105" t="n">
-        <v>5.72446458222222</v>
+        <v>4.48269770666667</v>
       </c>
       <c r="D105" t="s">
         <v>13</v>
@@ -1913,27 +1909,25 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1992</v>
+        <v>2024</v>
       </c>
       <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>5.97224082888889</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C106"/>
       <c r="D106" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1993</v>
+        <v>1990</v>
       </c>
       <c r="B107" t="s">
         <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>5.73746312333333</v>
+        <v>5.83332072888889</v>
       </c>
       <c r="D107" t="s">
         <v>13</v>
@@ -1941,13 +1935,13 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1994</v>
+        <v>1991</v>
       </c>
       <c r="B108" t="s">
         <v>16</v>
       </c>
       <c r="C108" t="n">
-        <v>6.67376381222222</v>
+        <v>5.72446458222222</v>
       </c>
       <c r="D108" t="s">
         <v>13</v>
@@ -1955,13 +1949,13 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1995</v>
+        <v>1992</v>
       </c>
       <c r="B109" t="s">
         <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>6.28264901</v>
+        <v>5.97224082888889</v>
       </c>
       <c r="D109" t="s">
         <v>13</v>
@@ -1969,13 +1963,13 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1996</v>
+        <v>1993</v>
       </c>
       <c r="B110" t="s">
         <v>16</v>
       </c>
       <c r="C110" t="n">
-        <v>6.54659740777778</v>
+        <v>5.73746312333333</v>
       </c>
       <c r="D110" t="s">
         <v>13</v>
@@ -1983,13 +1977,13 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1997</v>
+        <v>1994</v>
       </c>
       <c r="B111" t="s">
         <v>16</v>
       </c>
       <c r="C111" t="n">
-        <v>8.02545755</v>
+        <v>6.67376381222222</v>
       </c>
       <c r="D111" t="s">
         <v>13</v>
@@ -1997,13 +1991,13 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1998</v>
+        <v>1995</v>
       </c>
       <c r="B112" t="s">
         <v>16</v>
       </c>
       <c r="C112" t="n">
-        <v>6.79717775</v>
+        <v>6.28264901</v>
       </c>
       <c r="D112" t="s">
         <v>13</v>
@@ -2011,13 +2005,13 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="B113" t="s">
         <v>16</v>
       </c>
       <c r="C113" t="n">
-        <v>6.56662310333333</v>
+        <v>6.54659740777778</v>
       </c>
       <c r="D113" t="s">
         <v>13</v>
@@ -2025,13 +2019,13 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="B114" t="s">
         <v>16</v>
       </c>
       <c r="C114" t="n">
-        <v>6.15024223</v>
+        <v>8.02545755</v>
       </c>
       <c r="D114" t="s">
         <v>13</v>
@@ -2039,13 +2033,13 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="B115" t="s">
         <v>16</v>
       </c>
       <c r="C115" t="n">
-        <v>5.46468584444444</v>
+        <v>6.79717775</v>
       </c>
       <c r="D115" t="s">
         <v>13</v>
@@ -2053,13 +2047,13 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="B116" t="s">
         <v>16</v>
       </c>
       <c r="C116" t="n">
-        <v>6.09813719777778</v>
+        <v>6.56662310333333</v>
       </c>
       <c r="D116" t="s">
         <v>13</v>
@@ -2067,13 +2061,13 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="B117" t="s">
         <v>16</v>
       </c>
       <c r="C117" t="n">
-        <v>7.32654418222222</v>
+        <v>6.15024223</v>
       </c>
       <c r="D117" t="s">
         <v>13</v>
@@ -2081,13 +2075,13 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="B118" t="s">
         <v>16</v>
       </c>
       <c r="C118" t="n">
-        <v>6.44855184111111</v>
+        <v>5.46468584444444</v>
       </c>
       <c r="D118" t="s">
         <v>13</v>
@@ -2095,13 +2089,13 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="B119" t="s">
         <v>16</v>
       </c>
       <c r="C119" t="n">
-        <v>5.93542940222222</v>
+        <v>6.09813719777778</v>
       </c>
       <c r="D119" t="s">
         <v>13</v>
@@ -2109,13 +2103,13 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="B120" t="s">
         <v>16</v>
       </c>
       <c r="C120" t="n">
-        <v>6.03813544888889</v>
+        <v>7.32654418222222</v>
       </c>
       <c r="D120" t="s">
         <v>13</v>
@@ -2123,13 +2117,13 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="B121" t="s">
         <v>16</v>
       </c>
       <c r="C121" t="n">
-        <v>5.59726527555556</v>
+        <v>6.44855184111111</v>
       </c>
       <c r="D121" t="s">
         <v>13</v>
@@ -2137,13 +2131,13 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="B122" t="s">
         <v>16</v>
       </c>
       <c r="C122" t="n">
-        <v>5.95535531555555</v>
+        <v>5.93542940222222</v>
       </c>
       <c r="D122" t="s">
         <v>13</v>
@@ -2151,13 +2145,13 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="B123" t="s">
         <v>16</v>
       </c>
       <c r="C123" t="n">
-        <v>6.53957764777778</v>
+        <v>6.03813544888889</v>
       </c>
       <c r="D123" t="s">
         <v>13</v>
@@ -2165,13 +2159,13 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="B124" t="s">
         <v>16</v>
       </c>
       <c r="C124" t="n">
-        <v>6.52256541444444</v>
+        <v>5.59726527555556</v>
       </c>
       <c r="D124" t="s">
         <v>13</v>
@@ -2179,13 +2173,13 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="B125" t="s">
         <v>16</v>
       </c>
       <c r="C125" t="n">
-        <v>6.39720601666667</v>
+        <v>5.95535531555555</v>
       </c>
       <c r="D125" t="s">
         <v>13</v>
@@ -2193,13 +2187,13 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="B126" t="s">
         <v>16</v>
       </c>
       <c r="C126" t="n">
-        <v>6.68698877</v>
+        <v>6.53957764777778</v>
       </c>
       <c r="D126" t="s">
         <v>13</v>
@@ -2207,13 +2201,13 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="B127" t="s">
         <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>6.32413447111111</v>
+        <v>6.52256541444444</v>
       </c>
       <c r="D127" t="s">
         <v>13</v>
@@ -2221,13 +2215,13 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="B128" t="s">
         <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>6.41458419555555</v>
+        <v>6.39720601666667</v>
       </c>
       <c r="D128" t="s">
         <v>13</v>
@@ -2235,13 +2229,13 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="B129" t="s">
         <v>16</v>
       </c>
       <c r="C129" t="n">
-        <v>6.51736506666667</v>
+        <v>6.68698877</v>
       </c>
       <c r="D129" t="s">
         <v>13</v>
@@ -2249,13 +2243,13 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="B130" t="s">
         <v>16</v>
       </c>
       <c r="C130" t="n">
-        <v>5.38046835333333</v>
+        <v>6.32413447111111</v>
       </c>
       <c r="D130" t="s">
         <v>13</v>
@@ -2263,13 +2257,13 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="B131" t="s">
         <v>16</v>
       </c>
       <c r="C131" t="n">
-        <v>5.31162168777778</v>
+        <v>6.41458419555555</v>
       </c>
       <c r="D131" t="s">
         <v>13</v>
@@ -2277,13 +2271,13 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B132" t="s">
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>4.88558238666667</v>
+        <v>6.51736506666667</v>
       </c>
       <c r="D132" t="s">
         <v>13</v>
@@ -2291,13 +2285,13 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="B133" t="s">
         <v>16</v>
       </c>
       <c r="C133" t="n">
-        <v>4.89072432444444</v>
+        <v>5.38046835333333</v>
       </c>
       <c r="D133" t="s">
         <v>13</v>
@@ -2305,13 +2299,13 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="B134" t="s">
         <v>16</v>
       </c>
       <c r="C134" t="n">
-        <v>4.51983098111111</v>
+        <v>5.31162168777778</v>
       </c>
       <c r="D134" t="s">
         <v>13</v>
@@ -2319,13 +2313,13 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B135" t="s">
         <v>16</v>
       </c>
       <c r="C135" t="n">
-        <v>4.66049366444444</v>
+        <v>4.88558238666667</v>
       </c>
       <c r="D135" t="s">
         <v>13</v>
@@ -2333,13 +2327,13 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B136" t="s">
         <v>16</v>
       </c>
       <c r="C136" t="n">
-        <v>4.78886906666667</v>
+        <v>4.89072432444444</v>
       </c>
       <c r="D136" t="s">
         <v>13</v>
@@ -2347,13 +2341,13 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B137" t="s">
         <v>16</v>
       </c>
       <c r="C137" t="n">
-        <v>4.74901104333333</v>
+        <v>4.51983098111111</v>
       </c>
       <c r="D137" t="s">
         <v>13</v>
@@ -2361,55 +2355,63 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1990</v>
+        <v>2021</v>
       </c>
       <c r="B138" t="s">
-        <v>17</v>
-      </c>
-      <c r="C138"/>
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>4.66049366444444</v>
+      </c>
       <c r="D138" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1991</v>
+        <v>2022</v>
       </c>
       <c r="B139" t="s">
-        <v>17</v>
-      </c>
-      <c r="C139"/>
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>4.78886906666667</v>
+      </c>
       <c r="D139" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1992</v>
+        <v>2023</v>
       </c>
       <c r="B140" t="s">
-        <v>17</v>
-      </c>
-      <c r="C140"/>
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>4.74901104333333</v>
+      </c>
       <c r="D140" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1993</v>
+        <v>2024</v>
       </c>
       <c r="B141" t="s">
-        <v>17</v>
-      </c>
-      <c r="C141"/>
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>4.0304</v>
+      </c>
       <c r="D141" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1994</v>
+        <v>1990</v>
       </c>
       <c r="B142" t="s">
         <v>17</v>
@@ -2421,7 +2423,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1995</v>
+        <v>1991</v>
       </c>
       <c r="B143" t="s">
         <v>17</v>
@@ -2433,7 +2435,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1996</v>
+        <v>1992</v>
       </c>
       <c r="B144" t="s">
         <v>17</v>
@@ -2445,7 +2447,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1997</v>
+        <v>1993</v>
       </c>
       <c r="B145" t="s">
         <v>17</v>
@@ -2457,7 +2459,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1998</v>
+        <v>1994</v>
       </c>
       <c r="B146" t="s">
         <v>17</v>
@@ -2469,7 +2471,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1999</v>
+        <v>1995</v>
       </c>
       <c r="B147" t="s">
         <v>17</v>
@@ -2481,69 +2483,61 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2000</v>
+        <v>1996</v>
       </c>
       <c r="B148" t="s">
         <v>17</v>
       </c>
-      <c r="C148" t="n">
-        <v>-3.189723476</v>
-      </c>
+      <c r="C148"/>
       <c r="D148" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2001</v>
+        <v>1997</v>
       </c>
       <c r="B149" t="s">
         <v>17</v>
       </c>
-      <c r="C149" t="n">
-        <v>-3.237225273</v>
-      </c>
+      <c r="C149"/>
       <c r="D149" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2002</v>
+        <v>1998</v>
       </c>
       <c r="B150" t="s">
         <v>17</v>
       </c>
-      <c r="C150" t="n">
-        <v>-2.826985472</v>
-      </c>
+      <c r="C150"/>
       <c r="D150" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2003</v>
+        <v>1999</v>
       </c>
       <c r="B151" t="s">
         <v>17</v>
       </c>
-      <c r="C151" t="n">
-        <v>-1.69551247</v>
-      </c>
+      <c r="C151"/>
       <c r="D151" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="B152" t="s">
         <v>17</v>
       </c>
       <c r="C152" t="n">
-        <v>-1.643343893</v>
+        <v>-3.189723476</v>
       </c>
       <c r="D152" t="s">
         <v>13</v>
@@ -2551,13 +2545,13 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2005</v>
+        <v>2001</v>
       </c>
       <c r="B153" t="s">
         <v>17</v>
       </c>
       <c r="C153" t="n">
-        <v>-2.515143459</v>
+        <v>-3.237225273</v>
       </c>
       <c r="D153" t="s">
         <v>13</v>
@@ -2565,13 +2559,13 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="B154" t="s">
         <v>17</v>
       </c>
       <c r="C154" t="n">
-        <v>-2.623657723</v>
+        <v>-2.826985472</v>
       </c>
       <c r="D154" t="s">
         <v>13</v>
@@ -2579,13 +2573,13 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="B155" t="s">
         <v>17</v>
       </c>
       <c r="C155" t="n">
-        <v>-3.060232926</v>
+        <v>-1.69551247</v>
       </c>
       <c r="D155" t="s">
         <v>13</v>
@@ -2593,13 +2587,13 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="B156" t="s">
         <v>17</v>
       </c>
       <c r="C156" t="n">
-        <v>-3.104601804</v>
+        <v>-1.643343893</v>
       </c>
       <c r="D156" t="s">
         <v>13</v>
@@ -2607,13 +2601,13 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="B157" t="s">
         <v>17</v>
       </c>
       <c r="C157" t="n">
-        <v>-3.601196117</v>
+        <v>-2.515143459</v>
       </c>
       <c r="D157" t="s">
         <v>13</v>
@@ -2621,13 +2615,13 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="B158" t="s">
         <v>17</v>
       </c>
       <c r="C158" t="n">
-        <v>-4.11124993</v>
+        <v>-2.623657723</v>
       </c>
       <c r="D158" t="s">
         <v>13</v>
@@ -2635,13 +2629,13 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="B159" t="s">
         <v>17</v>
       </c>
       <c r="C159" t="n">
-        <v>-3.552026494</v>
+        <v>-3.060232926</v>
       </c>
       <c r="D159" t="s">
         <v>13</v>
@@ -2649,13 +2643,13 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="B160" t="s">
         <v>17</v>
       </c>
       <c r="C160" t="n">
-        <v>-3.333004702</v>
+        <v>-3.104601804</v>
       </c>
       <c r="D160" t="s">
         <v>13</v>
@@ -2663,13 +2657,13 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="B161" t="s">
         <v>17</v>
       </c>
       <c r="C161" t="n">
-        <v>-3.576404465</v>
+        <v>-3.601196117</v>
       </c>
       <c r="D161" t="s">
         <v>13</v>
@@ -2677,13 +2671,13 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="B162" t="s">
         <v>17</v>
       </c>
       <c r="C162" t="n">
-        <v>-3.174108356</v>
+        <v>-4.11124993</v>
       </c>
       <c r="D162" t="s">
         <v>13</v>
@@ -2691,13 +2685,13 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="B163" t="s">
         <v>17</v>
       </c>
       <c r="C163" t="n">
-        <v>-2.763972025</v>
+        <v>-3.552026494</v>
       </c>
       <c r="D163" t="s">
         <v>13</v>
@@ -2705,13 +2699,13 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="B164" t="s">
         <v>17</v>
       </c>
       <c r="C164" t="n">
-        <v>-3.482484216</v>
+        <v>-3.333004702</v>
       </c>
       <c r="D164" t="s">
         <v>13</v>
@@ -2719,13 +2713,13 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="B165" t="s">
         <v>17</v>
       </c>
       <c r="C165" t="n">
-        <v>-3.853011032</v>
+        <v>-3.576404465</v>
       </c>
       <c r="D165" t="s">
         <v>13</v>
@@ -2733,13 +2727,13 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B166" t="s">
         <v>17</v>
       </c>
       <c r="C166" t="n">
-        <v>-4.054526903</v>
+        <v>-3.174108356</v>
       </c>
       <c r="D166" t="s">
         <v>13</v>
@@ -2747,13 +2741,13 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="B167" t="s">
         <v>17</v>
       </c>
       <c r="C167" t="n">
-        <v>-3.49884012</v>
+        <v>-2.763972025</v>
       </c>
       <c r="D167" t="s">
         <v>13</v>
@@ -2761,13 +2755,13 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="B168" t="s">
         <v>17</v>
       </c>
       <c r="C168" t="n">
-        <v>-4.121601528</v>
+        <v>-3.482484216</v>
       </c>
       <c r="D168" t="s">
         <v>13</v>
@@ -2775,13 +2769,13 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="B169" t="s">
         <v>17</v>
       </c>
       <c r="C169" t="n">
-        <v>-3.75603238</v>
+        <v>-3.853011032</v>
       </c>
       <c r="D169" t="s">
         <v>13</v>
@@ -2789,13 +2783,13 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B170" t="s">
         <v>17</v>
       </c>
       <c r="C170" t="n">
-        <v>-4.209201465</v>
+        <v>-4.054526903</v>
       </c>
       <c r="D170" t="s">
         <v>13</v>
@@ -2803,13 +2797,13 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="B171" t="s">
         <v>17</v>
       </c>
       <c r="C171" t="n">
-        <v>-4.274392925</v>
+        <v>-3.49884012</v>
       </c>
       <c r="D171" t="s">
         <v>13</v>
@@ -2817,13 +2811,13 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1990</v>
+        <v>2020</v>
       </c>
       <c r="B172" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C172" t="n">
-        <v>2.0433631159</v>
+        <v>-4.121601528</v>
       </c>
       <c r="D172" t="s">
         <v>13</v>
@@ -2831,13 +2825,13 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1991</v>
+        <v>2021</v>
       </c>
       <c r="B173" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C173" t="n">
-        <v>2.0433631159</v>
+        <v>-3.75603238</v>
       </c>
       <c r="D173" t="s">
         <v>13</v>
@@ -2845,13 +2839,13 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1992</v>
+        <v>2022</v>
       </c>
       <c r="B174" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C174" t="n">
-        <v>2.0433631159</v>
+        <v>-4.209201465</v>
       </c>
       <c r="D174" t="s">
         <v>13</v>
@@ -2859,13 +2853,13 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1993</v>
+        <v>2023</v>
       </c>
       <c r="B175" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C175" t="n">
-        <v>2.0437983058</v>
+        <v>-4.274392925</v>
       </c>
       <c r="D175" t="s">
         <v>13</v>
@@ -2873,27 +2867,25 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>1994</v>
+        <v>2024</v>
       </c>
       <c r="B176" t="s">
-        <v>18</v>
-      </c>
-      <c r="C176" t="n">
-        <v>2.0434648546</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C176"/>
       <c r="D176" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1995</v>
+        <v>1990</v>
       </c>
       <c r="B177" t="s">
         <v>18</v>
       </c>
       <c r="C177" t="n">
-        <v>2.0490697304</v>
+        <v>2.0433631159</v>
       </c>
       <c r="D177" t="s">
         <v>13</v>
@@ -2901,13 +2893,13 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>1996</v>
+        <v>1991</v>
       </c>
       <c r="B178" t="s">
         <v>18</v>
       </c>
       <c r="C178" t="n">
-        <v>1.9215840777</v>
+        <v>2.0433631159</v>
       </c>
       <c r="D178" t="s">
         <v>13</v>
@@ -2915,13 +2907,13 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>1997</v>
+        <v>1992</v>
       </c>
       <c r="B179" t="s">
         <v>18</v>
       </c>
       <c r="C179" t="n">
-        <v>2.6114150926</v>
+        <v>2.0433631159</v>
       </c>
       <c r="D179" t="s">
         <v>13</v>
@@ -2929,13 +2921,13 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>1998</v>
+        <v>1993</v>
       </c>
       <c r="B180" t="s">
         <v>18</v>
       </c>
       <c r="C180" t="n">
-        <v>2.0554269438</v>
+        <v>2.0437983058</v>
       </c>
       <c r="D180" t="s">
         <v>13</v>
@@ -2943,13 +2935,13 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>1999</v>
+        <v>1994</v>
       </c>
       <c r="B181" t="s">
         <v>18</v>
       </c>
       <c r="C181" t="n">
-        <v>1.9590894193</v>
+        <v>2.0434648546</v>
       </c>
       <c r="D181" t="s">
         <v>13</v>
@@ -2957,13 +2949,13 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2000</v>
+        <v>1995</v>
       </c>
       <c r="B182" t="s">
         <v>18</v>
       </c>
       <c r="C182" t="n">
-        <v>1.9069416566</v>
+        <v>2.0490697304</v>
       </c>
       <c r="D182" t="s">
         <v>13</v>
@@ -2971,13 +2963,13 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2001</v>
+        <v>1996</v>
       </c>
       <c r="B183" t="s">
         <v>18</v>
       </c>
       <c r="C183" t="n">
-        <v>0.0414908781</v>
+        <v>1.9215840777</v>
       </c>
       <c r="D183" t="s">
         <v>13</v>
@@ -2985,13 +2977,13 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2002</v>
+        <v>1997</v>
       </c>
       <c r="B184" t="s">
         <v>18</v>
       </c>
       <c r="C184" t="n">
-        <v>0.4173127559</v>
+        <v>2.6114150926</v>
       </c>
       <c r="D184" t="s">
         <v>13</v>
@@ -2999,13 +2991,13 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2003</v>
+        <v>1998</v>
       </c>
       <c r="B185" t="s">
         <v>18</v>
       </c>
       <c r="C185" t="n">
-        <v>0.1446869938</v>
+        <v>2.0554269438</v>
       </c>
       <c r="D185" t="s">
         <v>13</v>
@@ -3013,13 +3005,13 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>2004</v>
+        <v>1999</v>
       </c>
       <c r="B186" t="s">
         <v>18</v>
       </c>
       <c r="C186" t="n">
-        <v>0.4149972961</v>
+        <v>1.9590894193</v>
       </c>
       <c r="D186" t="s">
         <v>13</v>
@@ -3027,13 +3019,13 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2005</v>
+        <v>2000</v>
       </c>
       <c r="B187" t="s">
         <v>18</v>
       </c>
       <c r="C187" t="n">
-        <v>0.2084003456</v>
+        <v>1.9069416566</v>
       </c>
       <c r="D187" t="s">
         <v>13</v>
@@ -3041,13 +3033,13 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2006</v>
+        <v>2001</v>
       </c>
       <c r="B188" t="s">
         <v>18</v>
       </c>
       <c r="C188" t="n">
-        <v>0.5039862511</v>
+        <v>0.0414908781</v>
       </c>
       <c r="D188" t="s">
         <v>13</v>
@@ -3055,13 +3047,13 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="B189" t="s">
         <v>18</v>
       </c>
       <c r="C189" t="n">
-        <v>0.0779010099</v>
+        <v>0.4173127559</v>
       </c>
       <c r="D189" t="s">
         <v>13</v>
@@ -3069,13 +3061,13 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="B190" t="s">
         <v>18</v>
       </c>
       <c r="C190" t="n">
-        <v>0.0658578881</v>
+        <v>0.1446869938</v>
       </c>
       <c r="D190" t="s">
         <v>13</v>
@@ -3083,13 +3075,13 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="B191" t="s">
         <v>18</v>
       </c>
       <c r="C191" t="n">
-        <v>0.3697694787</v>
+        <v>0.4149972961</v>
       </c>
       <c r="D191" t="s">
         <v>13</v>
@@ -3097,13 +3089,13 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="B192" t="s">
         <v>18</v>
       </c>
       <c r="C192" t="n">
-        <v>0.0789416009</v>
+        <v>0.2084003456</v>
       </c>
       <c r="D192" t="s">
         <v>13</v>
@@ -3111,13 +3103,13 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="B193" t="s">
         <v>18</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.4265301171</v>
+        <v>0.5039862511</v>
       </c>
       <c r="D193" t="s">
         <v>13</v>
@@ -3125,13 +3117,13 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="B194" t="s">
         <v>18</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.4169836245</v>
+        <v>0.0779010099</v>
       </c>
       <c r="D194" t="s">
         <v>13</v>
@@ -3139,13 +3131,13 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="B195" t="s">
         <v>18</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.4311134251</v>
+        <v>0.0658578881</v>
       </c>
       <c r="D195" t="s">
         <v>13</v>
@@ -3153,13 +3145,13 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="B196" t="s">
         <v>18</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.16765498</v>
+        <v>0.3697694787</v>
       </c>
       <c r="D196" t="s">
         <v>13</v>
@@ -3167,13 +3159,13 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="B197" t="s">
         <v>18</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.1514312642</v>
+        <v>0.0789416009</v>
       </c>
       <c r="D197" t="s">
         <v>13</v>
@@ -3181,13 +3173,13 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="B198" t="s">
         <v>18</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.1953683031</v>
+        <v>-0.4265301171</v>
       </c>
       <c r="D198" t="s">
         <v>13</v>
@@ -3195,13 +3187,13 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="B199" t="s">
         <v>18</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.2303205444</v>
+        <v>-0.4169836245</v>
       </c>
       <c r="D199" t="s">
         <v>13</v>
@@ -3209,13 +3201,13 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="B200" t="s">
         <v>18</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.0823342338</v>
+        <v>-0.4311134251</v>
       </c>
       <c r="D200" t="s">
         <v>13</v>
@@ -3223,13 +3215,13 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="B201" t="s">
         <v>18</v>
       </c>
       <c r="C201" t="n">
-        <v>0.0924906436</v>
+        <v>-0.16765498</v>
       </c>
       <c r="D201" t="s">
         <v>13</v>
@@ -3237,13 +3229,13 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="B202" t="s">
         <v>18</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.2050399692</v>
+        <v>-0.1514312642</v>
       </c>
       <c r="D202" t="s">
         <v>13</v>
@@ -3251,13 +3243,13 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="B203" t="s">
         <v>18</v>
       </c>
       <c r="C203" t="n">
-        <v>0.0570727035</v>
+        <v>-0.1953683031</v>
       </c>
       <c r="D203" t="s">
         <v>13</v>
@@ -3265,13 +3257,13 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="B204" t="s">
         <v>18</v>
       </c>
       <c r="C204" t="n">
-        <v>0.048607391</v>
+        <v>-0.2303205444</v>
       </c>
       <c r="D204" t="s">
         <v>13</v>
@@ -3279,15 +3271,85 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B205" t="s">
         <v>18</v>
       </c>
       <c r="C205" t="n">
+        <v>-0.0823342338</v>
+      </c>
+      <c r="D205" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B206" t="s">
+        <v>18</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.0924906436</v>
+      </c>
+      <c r="D206" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B207" t="s">
+        <v>18</v>
+      </c>
+      <c r="C207" t="n">
+        <v>-0.2050399692</v>
+      </c>
+      <c r="D207" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B208" t="s">
+        <v>18</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0.0570727035</v>
+      </c>
+      <c r="D208" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B209" t="s">
+        <v>18</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.048607391</v>
+      </c>
+      <c r="D209" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B210" t="s">
+        <v>18</v>
+      </c>
+      <c r="C210" t="n">
         <v>0.2389163739</v>
       </c>
-      <c r="D205" t="s">
+      <c r="D210" t="s">
         <v>13</v>
       </c>
     </row>
